--- a/Employee_Reports_wi48/Pathmapriyan Muruguppilla Q0579.xlsx
+++ b/Employee_Reports_wi48/Pathmapriyan Muruguppilla Q0579.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>-58</v>
+        <v>-61</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-60</v>
+        <v>-63</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="5" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>-55</v>
+        <v>-58</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-46</v>
+        <v>-49</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="5" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>-52</v>
+        <v>-55</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-61</v>
+        <v>-64</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>-54</v>
+        <v>-57</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>-54</v>
+        <v>-57</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="5" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>-45</v>
+        <v>-48</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="5" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
@@ -1264,11 +1264,11 @@
         </is>
       </c>
       <c r="H17" s="5" t="n">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
@@ -1313,11 +1313,11 @@
         </is>
       </c>
       <c r="H18" s="5" t="n">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
@@ -1362,11 +1362,11 @@
         </is>
       </c>
       <c r="H19" s="5" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
@@ -1411,11 +1411,11 @@
         </is>
       </c>
       <c r="H20" s="5" t="n">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
@@ -1460,11 +1460,11 @@
         </is>
       </c>
       <c r="H21" s="5" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
@@ -1509,11 +1509,11 @@
         </is>
       </c>
       <c r="H22" s="5" t="n">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
@@ -1558,11 +1558,11 @@
         </is>
       </c>
       <c r="H23" s="5" t="n">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
@@ -1607,11 +1607,11 @@
         </is>
       </c>
       <c r="H24" s="5" t="n">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
@@ -1644,11 +1644,11 @@
         </is>
       </c>
       <c r="H25" s="5" t="n">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
@@ -1693,11 +1693,11 @@
         </is>
       </c>
       <c r="H26" s="5" t="n">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
@@ -1742,11 +1742,11 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-284</v>
+        <v>-287</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -1792,11 +1792,11 @@
         </is>
       </c>
       <c r="H28" s="3" t="n">
-        <v>-402</v>
+        <v>-405</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -1841,11 +1841,11 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-425</v>
+        <v>-428</v>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -1890,11 +1890,11 @@
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-340</v>
+        <v>-343</v>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -1927,11 +1927,11 @@
         </is>
       </c>
       <c r="H31" s="3" t="n">
-        <v>-340</v>
+        <v>-343</v>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -1964,11 +1964,11 @@
         </is>
       </c>
       <c r="H32" s="5" t="n">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>7639</v>
+        <v>7636</v>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>7835</v>
+        <v>7832</v>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
